--- a/data/trans_bre/P0902-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P0902-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 10,95</t>
+          <t>4,68; 11,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 16,58</t>
+          <t>8,44; 16,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 18,57</t>
+          <t>10,14; 18,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,85; 19,09</t>
+          <t>10,22; 19,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,21; 80,45</t>
+          <t>28,3; 81,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,73; 81,35</t>
+          <t>31,21; 75,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,91; 101,84</t>
+          <t>45,39; 100,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,35; 80,01</t>
+          <t>33,37; 82,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,11</t>
+          <t>2,36; 5,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,09</t>
+          <t>3,26; 7,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,08</t>
+          <t>3,47; 7,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 6,09</t>
+          <t>-0,57; 6,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,18; 143,63</t>
+          <t>37,95; 136,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,22; 132,49</t>
+          <t>46,68; 126,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,18; 124,97</t>
+          <t>46,61; 129,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 81,24</t>
+          <t>-4,08; 82,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,41</t>
+          <t>0,92; 7,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 5,46</t>
+          <t>-1,67; 5,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,13</t>
+          <t>0,74; 7,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,26</t>
+          <t>-1,42; 4,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 249,11</t>
+          <t>11,07; 241,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 128,56</t>
+          <t>-22,14; 132,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 203,16</t>
+          <t>10,64; 218,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 68,86</t>
+          <t>-16,45; 68,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,88</t>
+          <t>4,93; 8,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,6</t>
+          <t>7,09; 10,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 10,17</t>
+          <t>6,66; 10,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,61</t>
+          <t>3,23; 9,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,09; 104,62</t>
+          <t>56,61; 108,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,13; 103,9</t>
+          <t>61,22; 103,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,94; 118,7</t>
+          <t>67,65; 119,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,71; 86,73</t>
+          <t>27,93; 92,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P0902-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P0902-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,66</t>
+          <t>15,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>59,01%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,1</t>
+          <t>4,9; 11,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 16,18</t>
+          <t>8,57; 16,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 18,7</t>
+          <t>9,47; 18,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,22; 19,6</t>
+          <t>10,74; 20,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,3; 81,88</t>
+          <t>29,02; 83,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,21; 75,92</t>
+          <t>33,67; 78,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,39; 100,76</t>
+          <t>40,14; 98,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,37; 82,08</t>
+          <t>37,52; 87,81</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,86</t>
+          <t>2,34; 6,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,04</t>
+          <t>3,22; 7,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,24</t>
+          <t>3,36; 7,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 6,18</t>
+          <t>1,97; 5,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,95; 136,34</t>
+          <t>40,3; 140,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,68; 126,43</t>
+          <t>44,02; 129,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,61; 129,12</t>
+          <t>47,25; 128,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 82,2</t>
+          <t>15,89; 60,99</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,02</t>
+          <t>0,92; 7,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,49</t>
+          <t>-1,5; 5,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,61</t>
+          <t>1,0; 7,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,2</t>
+          <t>-0,3; 5,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 241,12</t>
+          <t>16,72; 252,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 132,71</t>
+          <t>-21,09; 146,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 218,82</t>
+          <t>15,25; 211,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 68,46</t>
+          <t>-3,53; 88,96</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,14</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>56,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,03</t>
+          <t>4,94; 8,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,57</t>
+          <t>7,06; 10,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,13</t>
+          <t>6,77; 10,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,09</t>
+          <t>5,41; 8,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,61; 108,33</t>
+          <t>55,91; 108,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,22; 103,88</t>
+          <t>60,08; 107,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,65; 119,72</t>
+          <t>66,28; 118,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,93; 92,52</t>
+          <t>40,03; 73,03</t>
         </is>
       </c>
     </row>
